--- a/Archived_HE_Data/hedata_2026-08-04.xlsx
+++ b/Archived_HE_Data/hedata_2026-08-04.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd HH:mm:ss UTC"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F488"/>
+  <dimension ref="A1:F288"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="2" customWidth="1"/>
@@ -9003,6006 +9003,6 @@
         <v>46238</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F289" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F290" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F291" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F292" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F293" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F294" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F295" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F296" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F297" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F298" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F299" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F300" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F301" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F302" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F303" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F304" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F305" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F306" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F307" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F308" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F309" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F310" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F311" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F312" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F313" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F314" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F315" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F316" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F317" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F318" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F319" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F320" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F321" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F322" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F323" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F324" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F325" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F326" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F327" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F328" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F329" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F330" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F331" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F332" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F333" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F334" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F335" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F336" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F337" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F338" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F339" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E340" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F340" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F341" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E342" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F342" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E343" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F343" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F344" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F345" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E346" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F346" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E347" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F347" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F348" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F349" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F350" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F351" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F352" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F353" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F354" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E355" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F355" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E356" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F356" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F357" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F358" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F359" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E360" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F360" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F361" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F362" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F363" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F364" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F365" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F366" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F367" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E368" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F368" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F369" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E370" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F370" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F371" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F372" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F373" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F374" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F375" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F376" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F377" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F378" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F379" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F380" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F381" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F382" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F383" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F384" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F385" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F386" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F387" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F388" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F389" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F390" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F391" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F392" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F393" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F394" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F395" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F396" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F397" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E398" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F398" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F399" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F400" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F401" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F402" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F403" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F404" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F405" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F406" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F407" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F408" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F409" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F410" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E411" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F411" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E412" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F412" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F413" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F414" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F415" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F416" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F417" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F418" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F419" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F420" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F421" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F422" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F423" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F424" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F425" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F426" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F427" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F428" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F429" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F430" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F431" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F432" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F433" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F434" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F435" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F436" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F437" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F438" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F439" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F440" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F441" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F442" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F443" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F444" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F445" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E446" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F446" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E447" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F447" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F448" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F449" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E450" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F450" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E451" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F451" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F452" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E453" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F453" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E454" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F454" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F455" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F456" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F457" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F458" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F459" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F460" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F461" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F462" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F463" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>Assistant Professor - English</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261885</t>
-        </is>
-      </c>
-      <c r="F464" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Digital Engagement Intern</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261909</t>
-        </is>
-      </c>
-      <c r="F465" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Office Aide, Central Scheduling</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262026</t>
-        </is>
-      </c>
-      <c r="F466" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>Work Study - Business Office Aide, Shared Business Services</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E467" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262028</t>
-        </is>
-      </c>
-      <c r="F467" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Catering &amp; Events Staff</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E468" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/262036</t>
-        </is>
-      </c>
-      <c r="F468" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>Heavy Equipment Operator - Equipment Services</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E469" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261156</t>
-        </is>
-      </c>
-      <c r="F469" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>Business Manager - Engineering &amp; Physical Sciences Deans Office</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E470" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261375</t>
-        </is>
-      </c>
-      <c r="F470" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>Preventive Mt Technician - Preventive Maintenance</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E471" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261371</t>
-        </is>
-      </c>
-      <c r="F471" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Director, Creative Media-Football</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261665</t>
-        </is>
-      </c>
-      <c r="F472" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>Manager, Programming &amp; Operations - Wyoming Public Media (WPM)</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261884</t>
-        </is>
-      </c>
-      <c r="F473" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>Assistant Director, Development - Cowboy Joe Club</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261931</t>
-        </is>
-      </c>
-      <c r="F474" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>Office Associate, Senior - Institutional Advancement &amp; UW Foundation</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E475" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261938</t>
-        </is>
-      </c>
-      <c r="F475" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Compliance, Proposals, Agreements and Strategic Services Intern, Research Services  </t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E476" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261942</t>
-        </is>
-      </c>
-      <c r="F476" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Work Study - Campus Recreation, Facility Employee</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261944</t>
-        </is>
-      </c>
-      <c r="F477" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Enterprise Architect, Data and Reporting Manager - Security &amp; Networking</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E478" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261952</t>
-        </is>
-      </c>
-      <c r="F478" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Animal Research Compliance Coordinator - Compliance, Proposals, Agreements &amp; Strategic Services</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E479" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261971</t>
-        </is>
-      </c>
-      <c r="F479" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Work Study Posn Student - UWIN Makerspace Tech, Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261973</t>
-        </is>
-      </c>
-      <c r="F480" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Student Marketing Coordinator, Business Enterprises</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E481" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261985</t>
-        </is>
-      </c>
-      <c r="F481" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Library Aide, Library Coach (Peer Mentor), UW Libraries</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E482" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261972</t>
-        </is>
-      </c>
-      <c r="F482" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>Computer Maintenance Technician, Senior - Academic Technology Services</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E483" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261574</t>
-        </is>
-      </c>
-      <c r="F483" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>Asst Professor - Psychology</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261698</t>
-        </is>
-      </c>
-      <c r="F484" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Hourly Pooled- CASM Tutor, Mathematics &amp; Statistics</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261791</t>
-        </is>
-      </c>
-      <c r="F485" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Parking Services Officer</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261798</t>
-        </is>
-      </c>
-      <c r="F486" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>Hourly Pooled - Car Rental Attendant - Transportation Services</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261776</t>
-        </is>
-      </c>
-      <c r="F487" s="2">
-        <v>46238</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>Program Coordinator - Center for Assistance with Statistics and Mathematics (CASM)</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>Laramie, WY, United States</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>University of Wyoming</t>
-        </is>
-      </c>
-      <c r="E488" t="inlineStr">
-        <is>
-          <t>https://eeik.fa.us2.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/job/261775</t>
-        </is>
-      </c>
-      <c r="F488" s="2">
-        <v>46238</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
